--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678577</v>
       </c>
       <c r="B2" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129678525</v>
       </c>
       <c r="B3" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129678517</v>
       </c>
       <c r="B4" t="n">
-        <v>96245</v>
+        <v>96257</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129678534</v>
       </c>
       <c r="B5" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129678614</v>
       </c>
       <c r="B6" t="n">
-        <v>97011</v>
+        <v>97023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678577</v>
       </c>
       <c r="B2" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129678525</v>
       </c>
       <c r="B3" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129678517</v>
       </c>
       <c r="B4" t="n">
-        <v>96257</v>
+        <v>96258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129678534</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129678614</v>
       </c>
       <c r="B6" t="n">
-        <v>97023</v>
+        <v>97024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678577</v>
       </c>
       <c r="B2" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129678525</v>
       </c>
       <c r="B3" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129678517</v>
       </c>
       <c r="B4" t="n">
-        <v>96258</v>
+        <v>96263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129678534</v>
       </c>
       <c r="B5" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129678614</v>
       </c>
       <c r="B6" t="n">
-        <v>97024</v>
+        <v>97029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678577</v>
       </c>
       <c r="B2" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129678517</v>
       </c>
       <c r="B4" t="n">
-        <v>96263</v>
+        <v>96267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129678534</v>
       </c>
       <c r="B5" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129678614</v>
       </c>
       <c r="B6" t="n">
-        <v>97029</v>
+        <v>97033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678577</v>
       </c>
       <c r="B2" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129678517</v>
       </c>
       <c r="B4" t="n">
-        <v>96267</v>
+        <v>96269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129678534</v>
       </c>
       <c r="B5" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129678614</v>
       </c>
       <c r="B6" t="n">
-        <v>97033</v>
+        <v>97035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678577</v>
       </c>
       <c r="B2" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129678517</v>
       </c>
       <c r="B4" t="n">
-        <v>96269</v>
+        <v>96279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129678614</v>
       </c>
       <c r="B6" t="n">
-        <v>97035</v>
+        <v>97045</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678577</v>
       </c>
       <c r="B2" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129678525</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129678517</v>
       </c>
       <c r="B4" t="n">
-        <v>96279</v>
+        <v>96283</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129678534</v>
       </c>
       <c r="B5" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129678614</v>
       </c>
       <c r="B6" t="n">
-        <v>97045</v>
+        <v>97049</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678577</v>
       </c>
       <c r="B2" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129678525</v>
       </c>
       <c r="B3" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129678517</v>
       </c>
       <c r="B4" t="n">
-        <v>96283</v>
+        <v>96286</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129678534</v>
       </c>
       <c r="B5" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129678614</v>
       </c>
       <c r="B6" t="n">
-        <v>97049</v>
+        <v>97052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678577</v>
       </c>
       <c r="B2" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129678525</v>
       </c>
       <c r="B3" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129678517</v>
       </c>
       <c r="B4" t="n">
-        <v>96286</v>
+        <v>96287</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129678534</v>
       </c>
       <c r="B5" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129678614</v>
       </c>
       <c r="B6" t="n">
-        <v>97052</v>
+        <v>97053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678577</v>
       </c>
       <c r="B2" t="n">
-        <v>97044</v>
+        <v>97061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129678525</v>
       </c>
       <c r="B3" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129678517</v>
       </c>
       <c r="B4" t="n">
-        <v>96287</v>
+        <v>96304</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129678534</v>
       </c>
       <c r="B5" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>129678614</v>
       </c>
       <c r="B6" t="n">
-        <v>97053</v>
+        <v>97070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129678577</v>
       </c>
       <c r="B2" t="n">
-        <v>97061</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129678525</v>
+        <v>129678614</v>
       </c>
       <c r="B3" t="n">
-        <v>79708</v>
+        <v>97367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,32 +803,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stubbtrådmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscocephaloziopsis catenulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564702</v>
+        <v>564666</v>
       </c>
       <c r="R3" t="n">
-        <v>6511613</v>
+        <v>6511586</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,50 +902,50 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>William Rosén, Nina Gad Burgman, Mikael Burgman</t>
+          <t>William Rosén, Nina Gad Burgman, Mikael Burgman, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129678517</v>
+        <v>129678720</v>
       </c>
       <c r="B4" t="n">
-        <v>96304</v>
+        <v>92292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>1506</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med groddkorn</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564702</v>
+        <v>564704</v>
       </c>
       <c r="R4" t="n">
-        <v>6511613</v>
+        <v>6511514</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,6 +1010,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1019,17 +1039,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>William Rosén, Nina Gad Burgman, Mikael Burgman</t>
+          <t>William Rosén, Nina Gad Burgman, Mikael Burgman, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129678534</v>
+        <v>129678517</v>
       </c>
       <c r="B5" t="n">
-        <v>92905</v>
+        <v>96601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,32 +1057,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med groddkorn</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1106,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ljust mycel</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,32 +1163,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129678614</v>
+        <v>129678639</v>
       </c>
       <c r="B6" t="n">
-        <v>97070</v>
+        <v>97394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>291</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbtrådmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis catenulata</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,7 +1199,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>med groddkorn</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1193,13 +1208,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564666</v>
+        <v>564645</v>
       </c>
       <c r="R6" t="n">
-        <v>6511586</v>
+        <v>6511561</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,6 +1277,362 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129678534</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Jordbromossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>564702</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6511613</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ljust mycel</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>William Rosén, Nina Gad Burgman, Mikael Burgman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129678525</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Jordbromossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>564702</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6511613</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>William Rosén, Nina Gad Burgman, Mikael Burgman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129678669</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Jordbromossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>564630</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6511561</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>William Rosén, Nina Gad Burgman, Mikael Burgman, Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678577</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678614</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,6 +1058,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678720</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1160,6 +1180,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678517</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678639</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1399,6 +1429,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678534</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1516,6 +1551,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678525</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1633,8 +1673,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678669</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1559,38 +1559,40 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129678669</v>
+        <v>135791879</v>
       </c>
       <c r="B9" t="n">
-        <v>5179</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1604,10 +1606,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564630</v>
+        <v>564707</v>
       </c>
       <c r="R9" t="n">
-        <v>6511561</v>
+        <v>6511524</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1639,7 +1641,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1649,7 +1651,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ribghack runt gran. Trädet är i dagsläget dött och mycket av barnen har fallit av, men än syns tidigt de många ringhacken på kvarvarande barken.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,6 +1681,128 @@
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135791879</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129678669</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Jordbromossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>564630</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6511561</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>William Rosén, Nina Gad Burgman, Mikael Burgman, Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129678669</t>
         </is>
@@ -1689,6 +1818,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -1562,7 +1562,7 @@
         <v>135791879</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -1562,7 +1562,7 @@
         <v>135791879</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -1562,7 +1562,7 @@
         <v>135791879</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27912-2025 artfynd.xlsx
+++ b/artfynd/A 27912-2025 artfynd.xlsx
@@ -1562,7 +1562,7 @@
         <v>135791879</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
